--- a/data/trans_orig/IP22B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22B-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26679</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47884</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -1568,57 +1568,57 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>3433</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42668</t>
+          <t>43216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55577</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73147</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>43234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60754</t>
+          <t>61055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27319</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26451</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>29716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41828</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47412</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>65970</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>75664</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>138737</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>166567</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51411</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -5170,82 +5170,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5829</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54746</t>
+          <t>54806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67232</t>
+          <t>66700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>88386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>47492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75969</t>
+          <t>75137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97425</t>
+          <t>96902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27809</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20470</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26932</t>
+          <t>26775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>101451</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>140726</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>172175</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>96282</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>183464</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>215366</t>
+          <t>216016</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29535</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40158</t>
+          <t>40441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17010</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>19999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42750</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56847</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7118</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39325</t>
+          <t>39235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51922</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>76846</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86851</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>134029</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>158713</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>26716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,47 +13833,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4986</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31944</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>39693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57617</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>61777</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>78912</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>84973</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>131681</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>156877</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
